--- a/Kwartaalrapportage/VISMA/Q1 2026 Vehicles.xlsx
+++ b/Kwartaalrapportage/VISMA/Q1 2026 Vehicles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/VISMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_7D4BC39902D80C5747D2C0F60EC71AC7D78E09D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F62972E-BFD7-3449-B366-BA1932E6C123}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_7D4BC39902D80C5747D2C0F60EC71AC7D78E09D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D276B0BD-4819-2D4F-ABEE-4E87F385F036}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -364,7 +364,7 @@
     <numFmt numFmtId="164" formatCode="d\-m\-yyyy\ hh:mm"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\-#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -402,8 +402,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +437,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -602,7 +614,7 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="28">
       <alignment horizontal="left" vertical="top"/>
@@ -643,6 +655,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="43" applyFont="1" applyFill="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1144,11 +1159,12 @@
       <c r="E8" s="11">
         <v>0</v>
       </c>
-      <c r="F8" s="11">
-        <v>0</v>
+      <c r="F8" s="16">
+        <v>21008.54</v>
       </c>
       <c r="G8" s="11">
-        <v>-172838.62</v>
+        <f>-172838.62-F8</f>
+        <v>-193847.16</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="15"/>

--- a/Kwartaalrapportage/VISMA/Q1 2026 Vehicles.xlsx
+++ b/Kwartaalrapportage/VISMA/Q1 2026 Vehicles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/VISMA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommeijer/Git/Kwartaalrapportage/VISMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_7D4BC39902D80C5747D2C0F60EC71AC7D78E09D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D276B0BD-4819-2D4F-ABEE-4E87F385F036}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF80E1F1-6077-0B40-A075-BC74624F48D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,7 +1008,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -1018,7 +1018,7 @@
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>46134.2524619697</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1086,7 +1086,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1095,7 +1095,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
@@ -1143,7 +1143,7 @@
       <c r="J7" s="14"/>
       <c r="K7" s="15"/>
     </row>
-    <row r="8" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1169,7 +1169,7 @@
       <c r="J8" s="14"/>
       <c r="K8" s="15"/>
     </row>
-    <row r="9" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>16678.330000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>545885.85</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>33</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>-4.82</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>-413462</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>42</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>116640.65</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>46</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>54649.54</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>48</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>4455.51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>50</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>-1147873.92</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>67659.710000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>56</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>-228131</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>58</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>-240030.54</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>60</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>62</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>16721.330000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>64</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>-94827.04</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>66</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>76731.09</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>-16505.939999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
         <v>70</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>-79646.759999999995</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>73</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>4449.8999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="s">
         <v>76</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>78</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>2521.29</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
         <v>80</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>28445.32</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
         <v>82</v>
       </c>
@@ -1780,17 +1780,19 @@
       <c r="D35" s="11">
         <v>0</v>
       </c>
-      <c r="E35" s="11">
-        <v>37066.33</v>
+      <c r="E35" s="16">
+        <f>37066.33-6916.77-16525.46</f>
+        <v>13624.100000000002</v>
       </c>
       <c r="F35" s="11">
         <v>0</v>
       </c>
       <c r="G35" s="11">
-        <v>37066.33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+        <f>D35+E35-F35</f>
+        <v>13624.100000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
         <v>84</v>
       </c>
@@ -1813,7 +1815,7 @@
         <v>644.14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>86</v>
       </c>
@@ -1836,7 +1838,7 @@
         <v>12702.46</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
         <v>88</v>
       </c>
@@ -1859,7 +1861,7 @@
         <v>4280.68</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>90</v>
       </c>
@@ -1882,7 +1884,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>92</v>
       </c>
@@ -1905,7 +1907,7 @@
         <v>10161</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>94</v>
       </c>
@@ -1928,7 +1930,7 @@
         <v>726.83</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
         <v>96</v>
       </c>
@@ -1951,7 +1953,7 @@
         <v>-0.83</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>98</v>
       </c>
@@ -1974,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
         <v>100</v>
       </c>
@@ -1997,7 +1999,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
         <v>102</v>
       </c>
@@ -2020,7 +2022,7 @@
         <v>116.09</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
         <v>104</v>
       </c>
@@ -2043,7 +2045,7 @@
         <v>740.29</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="12" t="s">
